--- a/output/2020/sector_totals_2020.xlsx
+++ b/output/2020/sector_totals_2020.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1854.869201085222</v>
+        <v>1854.869197955685</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>705.2478320573083</v>
+        <v>696.3921821144685</v>
       </c>
       <c r="E3" t="n">
-        <v>408.3942545705854</v>
+        <v>409.5514588395075</v>
       </c>
       <c r="F3" t="n">
-        <v>82.30460461846388</v>
+        <v>83.19962909147142</v>
       </c>
       <c r="G3" t="n">
-        <v>4.458148208577082</v>
+        <v>4.424044057302067</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6445.426538678247</v>
+        <v>6445.42653554871</v>
       </c>
       <c r="C16" t="n">
         <v>541.6262477730177</v>
       </c>
       <c r="D16" t="n">
-        <v>5264.700490645991</v>
+        <v>5255.844840703151</v>
       </c>
       <c r="E16" t="n">
-        <v>7170.920611606466</v>
+        <v>7172.077815875388</v>
       </c>
       <c r="F16" t="n">
-        <v>4322.199540131975</v>
+        <v>4323.094564604983</v>
       </c>
       <c r="G16" t="n">
-        <v>40.08918433887719</v>
+        <v>40.05508018760217</v>
       </c>
     </row>
   </sheetData>

--- a/output/2020/sector_totals_2020.xlsx
+++ b/output/2020/sector_totals_2020.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1854.869197955685</v>
+        <v>1966.996522300945</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>696.3921821144685</v>
+        <v>777.1553833131068</v>
       </c>
       <c r="E3" t="n">
-        <v>409.5514588395075</v>
+        <v>2194.83914665772</v>
       </c>
       <c r="F3" t="n">
-        <v>83.19962909147142</v>
+        <v>195.0870449764647</v>
       </c>
       <c r="G3" t="n">
-        <v>4.424044057302067</v>
+        <v>85.86886720395711</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6445.42653554871</v>
+        <v>6557.55385989397</v>
       </c>
       <c r="C16" t="n">
         <v>541.6262477730177</v>
       </c>
       <c r="D16" t="n">
-        <v>5255.844840703151</v>
+        <v>5336.608041901789</v>
       </c>
       <c r="E16" t="n">
-        <v>7172.077815875388</v>
+        <v>8957.365503693603</v>
       </c>
       <c r="F16" t="n">
-        <v>4323.094564604983</v>
+        <v>4434.981980489976</v>
       </c>
       <c r="G16" t="n">
-        <v>40.05508018760217</v>
+        <v>121.4999033342572</v>
       </c>
     </row>
   </sheetData>

--- a/output/2020/sector_totals_2020.xlsx
+++ b/output/2020/sector_totals_2020.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1966.996522300945</v>
+        <v>1852.132527951331</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>114.8639943496143</v>
       </c>
       <c r="D3" t="n">
         <v>777.1553833131068</v>
@@ -817,16 +817,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6557.55385989397</v>
+        <v>6442.689865544356</v>
       </c>
       <c r="C16" t="n">
-        <v>541.6262477730177</v>
+        <v>656.490242122632</v>
       </c>
       <c r="D16" t="n">
         <v>5336.608041901789</v>
       </c>
       <c r="E16" t="n">
-        <v>8957.365503693603</v>
+        <v>8957.365503693602</v>
       </c>
       <c r="F16" t="n">
         <v>4434.981980489976</v>

--- a/output/2020/sector_totals_2020.xlsx
+++ b/output/2020/sector_totals_2020.xlsx
@@ -470,7 +470,7 @@
         <v>2898.9</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>357.167</v>
       </c>
       <c r="D2" t="n">
         <v>1717.2</v>
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1852.132527951331</v>
+        <v>1974.822167960878</v>
       </c>
       <c r="C3" t="n">
-        <v>114.8639943496143</v>
+        <v>122.6896400095471</v>
       </c>
       <c r="D3" t="n">
-        <v>777.1553833131068</v>
+        <v>782.6270591961262</v>
       </c>
       <c r="E3" t="n">
-        <v>2194.83914665772</v>
+        <v>2316.477991538866</v>
       </c>
       <c r="F3" t="n">
-        <v>195.0870449764647</v>
+        <v>202.8298615801357</v>
       </c>
       <c r="G3" t="n">
-        <v>85.86886720395711</v>
+        <v>91.41757940072117</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6442.689865544356</v>
+        <v>6565.379505553902</v>
       </c>
       <c r="C16" t="n">
-        <v>656.490242122632</v>
+        <v>1021.482887782565</v>
       </c>
       <c r="D16" t="n">
-        <v>5336.608041901789</v>
+        <v>5342.079717784808</v>
       </c>
       <c r="E16" t="n">
-        <v>8957.365503693602</v>
+        <v>9079.004348574748</v>
       </c>
       <c r="F16" t="n">
-        <v>4434.981980489976</v>
+        <v>4442.724797093647</v>
       </c>
       <c r="G16" t="n">
-        <v>121.4999033342572</v>
+        <v>127.0486155310213</v>
       </c>
     </row>
   </sheetData>
